--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008450004899078973</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23235748</v>
+        <v>4337510</v>
       </c>
       <c r="L2" t="n">
-        <v>13792948</v>
+        <v>2334032</v>
       </c>
       <c r="M2" t="n">
-        <v>3471827</v>
+        <v>528427</v>
       </c>
       <c r="N2" t="n">
-        <v>165429</v>
+        <v>15308</v>
       </c>
       <c r="O2" t="n">
-        <v>2059850</v>
+        <v>315091</v>
       </c>
       <c r="P2" t="n">
-        <v>817245</v>
+        <v>123608</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999223351478577</v>
+        <v>0.9998745322227478</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9186439514160156</v>
+        <v>0.8478354215621948</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8297979235649109</v>
+        <v>0.7023646235466003</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7892914414405823</v>
+        <v>0.6186380386352539</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4697512090206146</v>
+        <v>0.1464502066373825</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8294228315353394</v>
+        <v>0.680486261844635</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8780292272567749</v>
+        <v>0.7974709868431091</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026420486158906</v>
       </c>
       <c r="C3" t="n">
-        <v>1345</v>
+        <v>554</v>
       </c>
       <c r="D3" t="n">
-        <v>23235748</v>
+        <v>4337510</v>
       </c>
       <c r="E3" t="n">
-        <v>1875410</v>
+        <v>667472</v>
       </c>
       <c r="F3" t="n">
-        <v>25632</v>
+        <v>10580</v>
       </c>
       <c r="G3" t="n">
-        <v>2944</v>
+        <v>900</v>
       </c>
       <c r="H3" t="n">
-        <v>1389</v>
+        <v>551</v>
       </c>
       <c r="I3" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>50080658</v>
+        <v>10015830</v>
       </c>
       <c r="K3" t="n">
-        <v>54447679</v>
+        <v>10533556</v>
       </c>
       <c r="L3" t="n">
-        <v>62497715</v>
+        <v>12067099</v>
       </c>
       <c r="M3" t="n">
-        <v>76059868</v>
+        <v>15070430</v>
       </c>
       <c r="N3" t="n">
-        <v>81015619</v>
+        <v>16151123</v>
       </c>
       <c r="O3" t="n">
-        <v>78678510</v>
+        <v>15672101</v>
       </c>
       <c r="P3" t="n">
-        <v>80567888</v>
+        <v>16104815</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9241607189178467</v>
+        <v>0.864463746547699</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8450952172279358</v>
+        <v>0.7130240201950073</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7448201179504395</v>
+        <v>0.5661198496818542</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3712108433246613</v>
+        <v>0.1715028285980225</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8090959787368774</v>
+        <v>0.6183686852455139</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8454973101615906</v>
+        <v>0.6391544938087463</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03197089671244802</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1937213</v>
+        <v>735381</v>
       </c>
       <c r="E4" t="n">
-        <v>13792948</v>
+        <v>2334032</v>
       </c>
       <c r="F4" t="n">
-        <v>540009</v>
+        <v>181812</v>
       </c>
       <c r="G4" t="n">
-        <v>16558</v>
+        <v>7819</v>
       </c>
       <c r="H4" t="n">
-        <v>32061</v>
+        <v>13409</v>
       </c>
       <c r="I4" t="n">
-        <v>2386</v>
+        <v>974</v>
       </c>
       <c r="J4" t="n">
-        <v>2452</v>
+        <v>792</v>
       </c>
       <c r="K4" t="n">
-        <v>2057781</v>
+        <v>778471</v>
       </c>
       <c r="L4" t="n">
-        <v>2829109</v>
+        <v>989074</v>
       </c>
       <c r="M4" t="n">
-        <v>926836</v>
+        <v>325751</v>
       </c>
       <c r="N4" t="n">
-        <v>186734</v>
+        <v>89219</v>
       </c>
       <c r="O4" t="n">
-        <v>423624</v>
+        <v>147947</v>
       </c>
       <c r="P4" t="n">
-        <v>113527</v>
+        <v>31392</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999611973762512</v>
+        <v>0.9999372363090515</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9213940501213074</v>
+        <v>0.8560688495635986</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8373767137527466</v>
+        <v>0.7076542377471924</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7664112448692322</v>
+        <v>0.5912148952484131</v>
       </c>
       <c r="U4" t="n">
-        <v>0.414707750082016</v>
+        <v>0.1579895168542862</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8191333413124084</v>
+        <v>0.647942066192627</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8614562153816223</v>
+        <v>0.7095894813537598</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>857</v>
+        <v>172</v>
       </c>
       <c r="D5" t="n">
-        <v>74984</v>
+        <v>27733</v>
       </c>
       <c r="E5" t="n">
-        <v>820961</v>
+        <v>278361</v>
       </c>
       <c r="F5" t="n">
-        <v>3471827</v>
+        <v>528427</v>
       </c>
       <c r="G5" t="n">
-        <v>71010</v>
+        <v>30630</v>
       </c>
       <c r="H5" t="n">
-        <v>207520</v>
+        <v>62434</v>
       </c>
       <c r="I5" t="n">
-        <v>14137</v>
+        <v>5662</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1906792</v>
+        <v>680063</v>
       </c>
       <c r="L5" t="n">
-        <v>2528228</v>
+        <v>939395</v>
       </c>
       <c r="M5" t="n">
-        <v>1189469</v>
+        <v>404992</v>
       </c>
       <c r="N5" t="n">
-        <v>280218</v>
+        <v>73950</v>
       </c>
       <c r="O5" t="n">
-        <v>486016</v>
+        <v>194461</v>
       </c>
       <c r="P5" t="n">
-        <v>149340</v>
+        <v>69785</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999699592590332</v>
+        <v>0.9999514818191528</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9514431357383728</v>
+        <v>0.9106816053390503</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9343849420547485</v>
+        <v>0.8819034695625305</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9740801453590393</v>
+        <v>0.9552503824234009</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942809343338013</v>
+        <v>0.990007758140564</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9888589978218079</v>
+        <v>0.9790314435958862</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9967804551124573</v>
+        <v>0.9938040971755981</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>44890</v>
+        <v>14912</v>
       </c>
       <c r="E6" t="n">
-        <v>88725</v>
+        <v>19370</v>
       </c>
       <c r="F6" t="n">
-        <v>93550</v>
+        <v>27865</v>
       </c>
       <c r="G6" t="n">
-        <v>165429</v>
+        <v>15308</v>
       </c>
       <c r="H6" t="n">
-        <v>49393</v>
+        <v>10874</v>
       </c>
       <c r="I6" t="n">
-        <v>3490</v>
+        <v>894</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>41918</v>
+        <v>22729</v>
       </c>
       <c r="F7" t="n">
-        <v>258811</v>
+        <v>100751</v>
       </c>
       <c r="G7" t="n">
-        <v>91276</v>
+        <v>46717</v>
       </c>
       <c r="H7" t="n">
-        <v>2059850</v>
+        <v>315091</v>
       </c>
       <c r="I7" t="n">
-        <v>93442</v>
+        <v>23856</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>2095</v>
+        <v>1142</v>
       </c>
       <c r="F8" t="n">
-        <v>8834</v>
+        <v>4743</v>
       </c>
       <c r="G8" t="n">
-        <v>4946</v>
+        <v>3153</v>
       </c>
       <c r="H8" t="n">
-        <v>133261</v>
+        <v>60679</v>
       </c>
       <c r="I8" t="n">
-        <v>817245</v>
+        <v>123608</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
